--- a/data/trans_bre/P1409-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P1409-Clase-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,09</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>37,87%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,58</t>
+          <t>-1,7; 2,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 3,09</t>
+          <t>-1,25; 3,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 3,19</t>
+          <t>-1,01; 3,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-80,18; 430,82</t>
+          <t>-80,32; 314,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,41; 328,11</t>
+          <t>-53,84; 353,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-32,3; 136,26</t>
+          <t>-23,87; 172,46</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,91</t>
+          <t>2,19</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>44,17%</t>
+          <t>52,21%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,06; 5,28</t>
+          <t>0,13; 5,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 4,99</t>
+          <t>-0,45; 4,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 4,77</t>
+          <t>-1,02; 5,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-28,8; 729,42</t>
+          <t>-26,55; 795,5</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,71; 337,23</t>
+          <t>-22,35; 355,27</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,89; 166,24</t>
+          <t>-21,29; 188,98</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,25</t>
+          <t>1,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>126,48%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,11</t>
+          <t>-0,91; 4,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 5,23</t>
+          <t>-1,26; 5,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 5,68</t>
+          <t>-1,19; 4,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-50,76; 354,1</t>
+          <t>-45,42; 424,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-63,27; 480,04</t>
+          <t>-68,1; 493,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 764,78</t>
+          <t>-35,98; 226,36</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-0,09</t>
+          <t>0,83</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-2,44%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,37</t>
+          <t>-0,77; 2,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,64</t>
+          <t>-0,46; 2,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,64</t>
+          <t>-1,12; 2,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,13; 164,9</t>
+          <t>-31,86; 152,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-16,03; 178,87</t>
+          <t>-18,3; 157,13</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,45; 52,78</t>
+          <t>-23,89; 84,52</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,51</t>
+          <t>-0,35</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>105,69%</t>
+          <t>-6,5%</t>
         </is>
       </c>
     </row>
@@ -954,39 +954,39 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,12; 2,57</t>
+          <t>-1,2; 2,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 4,1</t>
+          <t>-0,57; 3,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 30,43</t>
+          <t>-3,13; 1,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-34,6; 187,21</t>
+          <t>-37,73; 196,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 171,24</t>
+          <t>-14,4; 161,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,05; 790,67</t>
+          <t>-42,06; 47,59</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,8</t>
+          <t>0,66</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 1,59</t>
+          <t>-2,29; 1,72</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 1,95</t>
+          <t>-4,34; 1,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 4,18</t>
+          <t>-7,57; 3,93</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-63,05; 138,85</t>
+          <t>-54,87; 161,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-53,46; 80,76</t>
+          <t>-57,19; 63,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-66,68; 1935,89</t>
+          <t>-66,56; 1772,53</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>23,56%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,57</t>
+          <t>0,09; 1,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,27</t>
+          <t>0,45; 2,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 11,0</t>
+          <t>-0,12; 1,83</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 98,02</t>
+          <t>2,27; 96,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,8; 104,87</t>
+          <t>15,47; 102,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,5; 344,79</t>
+          <t>-2,93; 55,55</t>
         </is>
       </c>
     </row>
